--- a/branches/dev/ValueSet-mii-vs-dokument-format-code.xlsx
+++ b/branches/dev/ValueSet-mii-vs-dokument-format-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T09:17:11+00:00</t>
+    <t>2026-09-13T10:28:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/ValueSet-mii-vs-dokument-format-code.xlsx
+++ b/branches/dev/ValueSet-mii-vs-dokument-format-code.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-13T10:28:40+00:00</t>
+    <t>2026-09-13T11:26:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
